--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -12934,7 +12934,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -13675,7 +13675,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -18043,7 +18043,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -18199,7 +18199,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -18472,7 +18472,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -18550,7 +18550,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -19213,7 +19213,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -19525,7 +19525,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -19915,7 +19915,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -20032,7 +20032,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -21007,7 +21007,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -21046,7 +21046,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -21163,7 +21163,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -21202,7 +21202,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -21631,7 +21631,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -22177,7 +22177,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -22567,7 +22567,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -22645,7 +22645,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -22918,7 +22918,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -23035,7 +23035,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -23113,7 +23113,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -23230,7 +23230,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -23308,7 +23308,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -23386,7 +23386,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -23581,7 +23581,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -23815,7 +23815,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -23971,7 +23971,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -24010,7 +24010,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -24049,7 +24049,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -24244,7 +24244,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -24283,7 +24283,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -24322,7 +24322,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -24595,7 +24595,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -24985,7 +24985,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -25024,7 +25024,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -25102,7 +25102,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -25141,7 +25141,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -25180,7 +25180,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -25453,7 +25453,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -25648,7 +25648,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -25765,7 +25765,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -25921,7 +25921,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -25999,7 +25999,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -26038,7 +26038,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -26155,7 +26155,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -26389,7 +26389,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -26506,7 +26506,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -26584,7 +26584,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/lam-mo-hinh-khu-cong-nghiep/</t>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-noi-that/</t>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -26701,7 +26701,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-biet-thu/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -26740,7 +26740,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/mo-hinh-cao-tang/</t>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -26818,7 +26818,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-van-chuyen-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/dich-vu-sua-chua-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -26935,7 +26935,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -26974,7 +26974,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org</t>
+          <t>https://mohinhkientruc.org/</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -27013,7 +27013,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>https://mohinhkientruc.org/xuong-san-xuat-mo-hinh/</t>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I683"/>
+  <dimension ref="A1:I705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27061,6 +27061,864 @@
         </is>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>1</v>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E684" t="n">
+        <v>43</v>
+      </c>
+      <c r="F684" t="n">
+        <v>3</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>6.98%</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>2</v>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E685" t="n">
+        <v>88</v>
+      </c>
+      <c r="F685" t="n">
+        <v>4</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>3</v>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>5</v>
+      </c>
+      <c r="E686" t="n">
+        <v>980</v>
+      </c>
+      <c r="F686" t="n">
+        <v>54</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>4</v>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>6</v>
+      </c>
+      <c r="E687" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F687" t="n">
+        <v>68</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>5</v>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>9</v>
+      </c>
+      <c r="E688" t="n">
+        <v>640</v>
+      </c>
+      <c r="F688" t="n">
+        <v>25</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>6</v>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>7</v>
+      </c>
+      <c r="E689" t="n">
+        <v>720</v>
+      </c>
+      <c r="F689" t="n">
+        <v>38</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>7</v>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>8</v>
+      </c>
+      <c r="E690" t="n">
+        <v>530</v>
+      </c>
+      <c r="F690" t="n">
+        <v>22</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>8</v>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>4</v>
+      </c>
+      <c r="E691" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F691" t="n">
+        <v>118</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>9</v>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E692" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F692" t="n">
+        <v>135</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>10</v>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E693" t="n">
+        <v>870</v>
+      </c>
+      <c r="F693" t="n">
+        <v>46</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>11</v>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E694" t="n">
+        <v>940</v>
+      </c>
+      <c r="F694" t="n">
+        <v>52</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>5.53%</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>12</v>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E695" t="n">
+        <v>480</v>
+      </c>
+      <c r="F695" t="n">
+        <v>18</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>13</v>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E696" t="n">
+        <v>2</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>14</v>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E697" t="n">
+        <v>590</v>
+      </c>
+      <c r="F697" t="n">
+        <v>26</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>15</v>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E698" t="n">
+        <v>820</v>
+      </c>
+      <c r="F698" t="n">
+        <v>45</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>16</v>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E699" t="n">
+        <v>760</v>
+      </c>
+      <c r="F699" t="n">
+        <v>38</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>17</v>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E700" t="n">
+        <v>930</v>
+      </c>
+      <c r="F700" t="n">
+        <v>58</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>18</v>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E701" t="n">
+        <v>880</v>
+      </c>
+      <c r="F701" t="n">
+        <v>52</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>19</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>45</v>
+      </c>
+      <c r="E702" t="n">
+        <v>24</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>20</v>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E703" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F703" t="n">
+        <v>168</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>21</v>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E704" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F704" t="n">
+        <v>121</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>22</v>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E705" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F705" t="n">
+        <v>104</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I705"/>
+  <dimension ref="A1:I727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27919,6 +27919,864 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>1</v>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E706" t="n">
+        <v>46</v>
+      </c>
+      <c r="F706" t="n">
+        <v>3</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>2</v>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E707" t="n">
+        <v>108</v>
+      </c>
+      <c r="F707" t="n">
+        <v>4</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>3</v>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>5</v>
+      </c>
+      <c r="E708" t="n">
+        <v>980</v>
+      </c>
+      <c r="F708" t="n">
+        <v>54</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>4</v>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>6</v>
+      </c>
+      <c r="E709" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F709" t="n">
+        <v>68</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>5</v>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>9</v>
+      </c>
+      <c r="E710" t="n">
+        <v>640</v>
+      </c>
+      <c r="F710" t="n">
+        <v>25</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>6</v>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>7</v>
+      </c>
+      <c r="E711" t="n">
+        <v>720</v>
+      </c>
+      <c r="F711" t="n">
+        <v>38</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>7</v>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>8</v>
+      </c>
+      <c r="E712" t="n">
+        <v>530</v>
+      </c>
+      <c r="F712" t="n">
+        <v>22</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>8</v>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>4</v>
+      </c>
+      <c r="E713" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F713" t="n">
+        <v>118</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>9</v>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E714" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F714" t="n">
+        <v>135</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>10</v>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E715" t="n">
+        <v>870</v>
+      </c>
+      <c r="F715" t="n">
+        <v>46</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>11</v>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E716" t="n">
+        <v>6</v>
+      </c>
+      <c r="F716" t="n">
+        <v>1</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>12</v>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E717" t="n">
+        <v>480</v>
+      </c>
+      <c r="F717" t="n">
+        <v>18</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>13</v>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E718" t="n">
+        <v>2</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>14</v>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E719" t="n">
+        <v>590</v>
+      </c>
+      <c r="F719" t="n">
+        <v>26</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>15</v>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E720" t="n">
+        <v>820</v>
+      </c>
+      <c r="F720" t="n">
+        <v>45</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>16</v>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E721" t="n">
+        <v>760</v>
+      </c>
+      <c r="F721" t="n">
+        <v>38</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>17</v>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E722" t="n">
+        <v>930</v>
+      </c>
+      <c r="F722" t="n">
+        <v>58</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>18</v>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E723" t="n">
+        <v>880</v>
+      </c>
+      <c r="F723" t="n">
+        <v>52</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>19</v>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E724" t="n">
+        <v>25</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>20</v>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E725" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F725" t="n">
+        <v>168</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>21</v>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E726" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F726" t="n">
+        <v>121</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>22</v>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E727" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F727" t="n">
+        <v>104</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I727"/>
+  <dimension ref="A1:I749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27135,7 +27135,7 @@
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -27174,7 +27174,7 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -27213,7 +27213,7 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>❓ People Also Ask</t>
         </is>
       </c>
     </row>
@@ -27252,7 +27252,7 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🔗 Organic Sitelinks</t>
         </is>
       </c>
     </row>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -27330,7 +27330,7 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -27369,7 +27369,7 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>🖼️ Image Pack</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -27408,7 +27408,7 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -27447,7 +27447,7 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>❓ People Also Ask</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27486,7 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🔗 Organic Sitelinks</t>
         </is>
       </c>
     </row>
@@ -27564,7 +27564,7 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -27642,7 +27642,7 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -27720,7 +27720,7 @@
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>❓ People Also Ask</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -27798,7 +27798,7 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>🖼️ Image Pack</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -27837,7 +27837,7 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🔗 Organic Sitelinks</t>
         </is>
       </c>
     </row>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -28032,7 +28032,7 @@
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -28071,7 +28071,7 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>❓ People Also Ask</t>
         </is>
       </c>
     </row>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🔗 Organic Sitelinks</t>
         </is>
       </c>
     </row>
@@ -28149,7 +28149,7 @@
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -28188,7 +28188,7 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>🖼️ Image Pack</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28266,7 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -28305,7 +28305,7 @@
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>❓ People Also Ask</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28344,7 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -28383,7 +28383,7 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🔗 Organic Sitelinks</t>
         </is>
       </c>
     </row>
@@ -28422,7 +28422,7 @@
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -28461,7 +28461,7 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -28500,7 +28500,7 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -28539,7 +28539,7 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -28578,7 +28578,7 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>❓ People Also Ask</t>
         </is>
       </c>
     </row>
@@ -28617,7 +28617,7 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28656,7 @@
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>🖼️ Image Pack</t>
+          <t>📌 Local Map Pack</t>
         </is>
       </c>
     </row>
@@ -28695,7 +28695,7 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🌟 Featured Snippet</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🖼️ Image Pack</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28773,865 @@
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>Standard Snippet</t>
+          <t>🔗 Organic Sitelinks</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>1</v>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E728" t="n">
+        <v>46</v>
+      </c>
+      <c r="F728" t="n">
+        <v>3</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>2</v>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E729" t="n">
+        <v>116</v>
+      </c>
+      <c r="F729" t="n">
+        <v>4</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>🌟 Featured Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>3</v>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>5</v>
+      </c>
+      <c r="E730" t="n">
+        <v>980</v>
+      </c>
+      <c r="F730" t="n">
+        <v>54</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>📌 Local Map Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>4</v>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>6</v>
+      </c>
+      <c r="E731" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F731" t="n">
+        <v>68</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>❓ People Also Ask</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>5</v>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>9</v>
+      </c>
+      <c r="E732" t="n">
+        <v>640</v>
+      </c>
+      <c r="F732" t="n">
+        <v>25</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>🔗 Organic Sitelinks</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>6</v>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>7</v>
+      </c>
+      <c r="E733" t="n">
+        <v>720</v>
+      </c>
+      <c r="F733" t="n">
+        <v>38</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>7</v>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>8</v>
+      </c>
+      <c r="E734" t="n">
+        <v>530</v>
+      </c>
+      <c r="F734" t="n">
+        <v>22</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>🌟 Featured Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>8</v>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>4</v>
+      </c>
+      <c r="E735" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F735" t="n">
+        <v>118</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>🌟 Featured Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>9</v>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E736" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F736" t="n">
+        <v>135</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>📌 Local Map Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>10</v>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E737" t="n">
+        <v>870</v>
+      </c>
+      <c r="F737" t="n">
+        <v>46</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>❓ People Also Ask</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>11</v>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E738" t="n">
+        <v>8</v>
+      </c>
+      <c r="F738" t="n">
+        <v>1</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>12</v>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E739" t="n">
+        <v>480</v>
+      </c>
+      <c r="F739" t="n">
+        <v>18</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>🔗 Organic Sitelinks</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>13</v>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E740" t="n">
+        <v>2</v>
+      </c>
+      <c r="F740" t="n">
+        <v>1</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>14</v>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E741" t="n">
+        <v>590</v>
+      </c>
+      <c r="F741" t="n">
+        <v>26</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>📌 Local Map Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>15</v>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E742" t="n">
+        <v>820</v>
+      </c>
+      <c r="F742" t="n">
+        <v>45</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>📌 Local Map Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>16</v>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E743" t="n">
+        <v>760</v>
+      </c>
+      <c r="F743" t="n">
+        <v>38</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>17</v>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E744" t="n">
+        <v>930</v>
+      </c>
+      <c r="F744" t="n">
+        <v>58</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>❓ People Also Ask</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>18</v>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E745" t="n">
+        <v>880</v>
+      </c>
+      <c r="F745" t="n">
+        <v>52</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>🌟 Featured Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>19</v>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E746" t="n">
+        <v>26</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>📌 Local Map Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>20</v>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E747" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F747" t="n">
+        <v>168</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>🌟 Featured Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>21</v>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E748" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F748" t="n">
+        <v>121</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>22</v>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E749" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F749" t="n">
+        <v>104</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>🔗 Organic Sitelinks</t>
         </is>
       </c>
     </row>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I749"/>
+  <dimension ref="A1:I771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29635,6 +29635,864 @@
         </is>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>1</v>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E750" t="n">
+        <v>46</v>
+      </c>
+      <c r="F750" t="n">
+        <v>3</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>2</v>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E751" t="n">
+        <v>116</v>
+      </c>
+      <c r="F751" t="n">
+        <v>4</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>3</v>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>5</v>
+      </c>
+      <c r="E752" t="n">
+        <v>980</v>
+      </c>
+      <c r="F752" t="n">
+        <v>54</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>4</v>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>6</v>
+      </c>
+      <c r="E753" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F753" t="n">
+        <v>68</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>5</v>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>9</v>
+      </c>
+      <c r="E754" t="n">
+        <v>640</v>
+      </c>
+      <c r="F754" t="n">
+        <v>25</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>6</v>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>7</v>
+      </c>
+      <c r="E755" t="n">
+        <v>720</v>
+      </c>
+      <c r="F755" t="n">
+        <v>38</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>7</v>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>8</v>
+      </c>
+      <c r="E756" t="n">
+        <v>530</v>
+      </c>
+      <c r="F756" t="n">
+        <v>22</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>8</v>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>4</v>
+      </c>
+      <c r="E757" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F757" t="n">
+        <v>118</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>9</v>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E758" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F758" t="n">
+        <v>135</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>10</v>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E759" t="n">
+        <v>870</v>
+      </c>
+      <c r="F759" t="n">
+        <v>46</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>11</v>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E760" t="n">
+        <v>8</v>
+      </c>
+      <c r="F760" t="n">
+        <v>1</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>12</v>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E761" t="n">
+        <v>480</v>
+      </c>
+      <c r="F761" t="n">
+        <v>18</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>13</v>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E762" t="n">
+        <v>2</v>
+      </c>
+      <c r="F762" t="n">
+        <v>1</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>14</v>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E763" t="n">
+        <v>590</v>
+      </c>
+      <c r="F763" t="n">
+        <v>26</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>15</v>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E764" t="n">
+        <v>820</v>
+      </c>
+      <c r="F764" t="n">
+        <v>45</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>16</v>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E765" t="n">
+        <v>760</v>
+      </c>
+      <c r="F765" t="n">
+        <v>38</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>17</v>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E766" t="n">
+        <v>930</v>
+      </c>
+      <c r="F766" t="n">
+        <v>58</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>18</v>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E767" t="n">
+        <v>880</v>
+      </c>
+      <c r="F767" t="n">
+        <v>52</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>19</v>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E768" t="n">
+        <v>26</v>
+      </c>
+      <c r="F768" t="n">
+        <v>0</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>20</v>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E769" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F769" t="n">
+        <v>168</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>21</v>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E770" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F770" t="n">
+        <v>121</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>22</v>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E771" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F771" t="n">
+        <v>104</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I771"/>
+  <dimension ref="A1:I793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30493,6 +30493,864 @@
         </is>
       </c>
     </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>1</v>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E772" t="n">
+        <v>46</v>
+      </c>
+      <c r="F772" t="n">
+        <v>3</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>2</v>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E773" t="n">
+        <v>118</v>
+      </c>
+      <c r="F773" t="n">
+        <v>4</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>3</v>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>5</v>
+      </c>
+      <c r="E774" t="n">
+        <v>980</v>
+      </c>
+      <c r="F774" t="n">
+        <v>54</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>4</v>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>6</v>
+      </c>
+      <c r="E775" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F775" t="n">
+        <v>68</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>5</v>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>9</v>
+      </c>
+      <c r="E776" t="n">
+        <v>640</v>
+      </c>
+      <c r="F776" t="n">
+        <v>25</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>6</v>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>7</v>
+      </c>
+      <c r="E777" t="n">
+        <v>720</v>
+      </c>
+      <c r="F777" t="n">
+        <v>38</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>7</v>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>8</v>
+      </c>
+      <c r="E778" t="n">
+        <v>530</v>
+      </c>
+      <c r="F778" t="n">
+        <v>22</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>8</v>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>4</v>
+      </c>
+      <c r="E779" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F779" t="n">
+        <v>118</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>9</v>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E780" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F780" t="n">
+        <v>135</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>10</v>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E781" t="n">
+        <v>870</v>
+      </c>
+      <c r="F781" t="n">
+        <v>46</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>11</v>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D782" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E782" t="n">
+        <v>8</v>
+      </c>
+      <c r="F782" t="n">
+        <v>1</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>12</v>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D783" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E783" t="n">
+        <v>480</v>
+      </c>
+      <c r="F783" t="n">
+        <v>18</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>13</v>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D784" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E784" t="n">
+        <v>3</v>
+      </c>
+      <c r="F784" t="n">
+        <v>1</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>14</v>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D785" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E785" t="n">
+        <v>590</v>
+      </c>
+      <c r="F785" t="n">
+        <v>26</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>15</v>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D786" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E786" t="n">
+        <v>820</v>
+      </c>
+      <c r="F786" t="n">
+        <v>45</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>16</v>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D787" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E787" t="n">
+        <v>760</v>
+      </c>
+      <c r="F787" t="n">
+        <v>38</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>17</v>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D788" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E788" t="n">
+        <v>930</v>
+      </c>
+      <c r="F788" t="n">
+        <v>58</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>18</v>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D789" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E789" t="n">
+        <v>880</v>
+      </c>
+      <c r="F789" t="n">
+        <v>52</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>19</v>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D790" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E790" t="n">
+        <v>26</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>20</v>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D791" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E791" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F791" t="n">
+        <v>168</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>21</v>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D792" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E792" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F792" t="n">
+        <v>121</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>22</v>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D793" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E793" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F793" t="n">
+        <v>104</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I793"/>
+  <dimension ref="A1:I837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31351,6 +31351,1722 @@
         </is>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>1</v>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D794" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E794" t="n">
+        <v>49</v>
+      </c>
+      <c r="F794" t="n">
+        <v>3</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>6.12%</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>2</v>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D795" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E795" t="n">
+        <v>128</v>
+      </c>
+      <c r="F795" t="n">
+        <v>4</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>3</v>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D796" t="n">
+        <v>5</v>
+      </c>
+      <c r="E796" t="n">
+        <v>980</v>
+      </c>
+      <c r="F796" t="n">
+        <v>54</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>4</v>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D797" t="n">
+        <v>6</v>
+      </c>
+      <c r="E797" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F797" t="n">
+        <v>68</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B798" t="n">
+        <v>5</v>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>9</v>
+      </c>
+      <c r="E798" t="n">
+        <v>640</v>
+      </c>
+      <c r="F798" t="n">
+        <v>25</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B799" t="n">
+        <v>6</v>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>7</v>
+      </c>
+      <c r="E799" t="n">
+        <v>720</v>
+      </c>
+      <c r="F799" t="n">
+        <v>38</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B800" t="n">
+        <v>7</v>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>8</v>
+      </c>
+      <c r="E800" t="n">
+        <v>530</v>
+      </c>
+      <c r="F800" t="n">
+        <v>22</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B801" t="n">
+        <v>8</v>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
+        <v>4</v>
+      </c>
+      <c r="E801" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F801" t="n">
+        <v>118</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B802" t="n">
+        <v>9</v>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D802" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E802" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F802" t="n">
+        <v>135</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B803" t="n">
+        <v>10</v>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D803" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E803" t="n">
+        <v>870</v>
+      </c>
+      <c r="F803" t="n">
+        <v>46</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B804" t="n">
+        <v>11</v>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D804" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E804" t="n">
+        <v>9</v>
+      </c>
+      <c r="F804" t="n">
+        <v>1</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>12</v>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D805" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E805" t="n">
+        <v>480</v>
+      </c>
+      <c r="F805" t="n">
+        <v>18</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>13</v>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D806" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E806" t="n">
+        <v>3</v>
+      </c>
+      <c r="F806" t="n">
+        <v>1</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>14</v>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E807" t="n">
+        <v>590</v>
+      </c>
+      <c r="F807" t="n">
+        <v>26</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>15</v>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E808" t="n">
+        <v>820</v>
+      </c>
+      <c r="F808" t="n">
+        <v>45</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>16</v>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E809" t="n">
+        <v>760</v>
+      </c>
+      <c r="F809" t="n">
+        <v>38</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>17</v>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E810" t="n">
+        <v>930</v>
+      </c>
+      <c r="F810" t="n">
+        <v>58</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>18</v>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E811" t="n">
+        <v>880</v>
+      </c>
+      <c r="F811" t="n">
+        <v>52</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>19</v>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D812" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E812" t="n">
+        <v>32</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>20</v>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D813" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E813" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F813" t="n">
+        <v>168</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>21</v>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D814" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E814" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F814" t="n">
+        <v>121</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B815" t="n">
+        <v>22</v>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D815" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E815" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F815" t="n">
+        <v>104</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B816" t="n">
+        <v>1</v>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D816" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E816" t="n">
+        <v>50</v>
+      </c>
+      <c r="F816" t="n">
+        <v>4</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>2</v>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D817" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E817" t="n">
+        <v>133</v>
+      </c>
+      <c r="F817" t="n">
+        <v>5</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>3</v>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D818" t="n">
+        <v>5</v>
+      </c>
+      <c r="E818" t="n">
+        <v>980</v>
+      </c>
+      <c r="F818" t="n">
+        <v>54</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>4</v>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D819" t="n">
+        <v>6</v>
+      </c>
+      <c r="E819" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F819" t="n">
+        <v>68</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>5</v>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D820" t="n">
+        <v>9</v>
+      </c>
+      <c r="E820" t="n">
+        <v>640</v>
+      </c>
+      <c r="F820" t="n">
+        <v>25</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>6</v>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D821" t="n">
+        <v>7</v>
+      </c>
+      <c r="E821" t="n">
+        <v>720</v>
+      </c>
+      <c r="F821" t="n">
+        <v>38</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>7</v>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D822" t="n">
+        <v>8</v>
+      </c>
+      <c r="E822" t="n">
+        <v>530</v>
+      </c>
+      <c r="F822" t="n">
+        <v>22</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>8</v>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D823" t="n">
+        <v>4</v>
+      </c>
+      <c r="E823" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F823" t="n">
+        <v>118</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>9</v>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D824" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E824" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F824" t="n">
+        <v>135</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>10</v>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D825" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E825" t="n">
+        <v>870</v>
+      </c>
+      <c r="F825" t="n">
+        <v>46</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>11</v>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D826" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E826" t="n">
+        <v>11</v>
+      </c>
+      <c r="F826" t="n">
+        <v>1</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>9.09%</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>12</v>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D827" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E827" t="n">
+        <v>480</v>
+      </c>
+      <c r="F827" t="n">
+        <v>18</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>13</v>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D828" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E828" t="n">
+        <v>3</v>
+      </c>
+      <c r="F828" t="n">
+        <v>1</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>14</v>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D829" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E829" t="n">
+        <v>590</v>
+      </c>
+      <c r="F829" t="n">
+        <v>26</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>15</v>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D830" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E830" t="n">
+        <v>820</v>
+      </c>
+      <c r="F830" t="n">
+        <v>45</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>16</v>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D831" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E831" t="n">
+        <v>760</v>
+      </c>
+      <c r="F831" t="n">
+        <v>38</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>17</v>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D832" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E832" t="n">
+        <v>930</v>
+      </c>
+      <c r="F832" t="n">
+        <v>58</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>18</v>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D833" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E833" t="n">
+        <v>880</v>
+      </c>
+      <c r="F833" t="n">
+        <v>52</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>19</v>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D834" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E834" t="n">
+        <v>34</v>
+      </c>
+      <c r="F834" t="n">
+        <v>0</v>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>20</v>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D835" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E835" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F835" t="n">
+        <v>168</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>21</v>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D836" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E836" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F836" t="n">
+        <v>121</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>22</v>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D837" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E837" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F837" t="n">
+        <v>104</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/song_anh_seo_keywords_historical_database.xlsx
+++ b/song_anh_seo_keywords_historical_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I837"/>
+  <dimension ref="A1:I925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33067,6 +33067,3438 @@
         </is>
       </c>
     </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>1</v>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D838" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E838" t="n">
+        <v>50</v>
+      </c>
+      <c r="F838" t="n">
+        <v>4</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>2</v>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D839" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E839" t="n">
+        <v>135</v>
+      </c>
+      <c r="F839" t="n">
+        <v>5</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>3.70%</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>3</v>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D840" t="n">
+        <v>5</v>
+      </c>
+      <c r="E840" t="n">
+        <v>980</v>
+      </c>
+      <c r="F840" t="n">
+        <v>54</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>4</v>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D841" t="n">
+        <v>6</v>
+      </c>
+      <c r="E841" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F841" t="n">
+        <v>68</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>5</v>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D842" t="n">
+        <v>9</v>
+      </c>
+      <c r="E842" t="n">
+        <v>640</v>
+      </c>
+      <c r="F842" t="n">
+        <v>25</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>6</v>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D843" t="n">
+        <v>7</v>
+      </c>
+      <c r="E843" t="n">
+        <v>720</v>
+      </c>
+      <c r="F843" t="n">
+        <v>38</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>7</v>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D844" t="n">
+        <v>8</v>
+      </c>
+      <c r="E844" t="n">
+        <v>530</v>
+      </c>
+      <c r="F844" t="n">
+        <v>22</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>8</v>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D845" t="n">
+        <v>4</v>
+      </c>
+      <c r="E845" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F845" t="n">
+        <v>118</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>9</v>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D846" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E846" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F846" t="n">
+        <v>135</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>10</v>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D847" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E847" t="n">
+        <v>870</v>
+      </c>
+      <c r="F847" t="n">
+        <v>46</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>11</v>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D848" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E848" t="n">
+        <v>12</v>
+      </c>
+      <c r="F848" t="n">
+        <v>1</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>8.33%</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>12</v>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D849" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E849" t="n">
+        <v>480</v>
+      </c>
+      <c r="F849" t="n">
+        <v>18</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>13</v>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D850" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E850" t="n">
+        <v>3</v>
+      </c>
+      <c r="F850" t="n">
+        <v>1</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>14</v>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D851" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E851" t="n">
+        <v>590</v>
+      </c>
+      <c r="F851" t="n">
+        <v>26</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>15</v>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D852" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E852" t="n">
+        <v>820</v>
+      </c>
+      <c r="F852" t="n">
+        <v>45</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>16</v>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D853" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E853" t="n">
+        <v>760</v>
+      </c>
+      <c r="F853" t="n">
+        <v>38</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>17</v>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D854" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E854" t="n">
+        <v>930</v>
+      </c>
+      <c r="F854" t="n">
+        <v>58</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>18</v>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D855" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E855" t="n">
+        <v>880</v>
+      </c>
+      <c r="F855" t="n">
+        <v>52</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>19</v>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D856" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E856" t="n">
+        <v>34</v>
+      </c>
+      <c r="F856" t="n">
+        <v>0</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>20</v>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D857" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E857" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F857" t="n">
+        <v>168</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>21</v>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D858" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E858" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F858" t="n">
+        <v>121</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>22</v>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D859" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E859" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F859" t="n">
+        <v>104</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>1</v>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E860" t="n">
+        <v>50</v>
+      </c>
+      <c r="F860" t="n">
+        <v>4</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>2</v>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E861" t="n">
+        <v>158</v>
+      </c>
+      <c r="F861" t="n">
+        <v>5</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>3</v>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>5</v>
+      </c>
+      <c r="E862" t="n">
+        <v>980</v>
+      </c>
+      <c r="F862" t="n">
+        <v>54</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>4</v>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>6</v>
+      </c>
+      <c r="E863" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F863" t="n">
+        <v>68</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>5</v>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D864" t="n">
+        <v>9</v>
+      </c>
+      <c r="E864" t="n">
+        <v>640</v>
+      </c>
+      <c r="F864" t="n">
+        <v>25</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>6</v>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>7</v>
+      </c>
+      <c r="E865" t="n">
+        <v>720</v>
+      </c>
+      <c r="F865" t="n">
+        <v>38</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>7</v>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D866" t="n">
+        <v>8</v>
+      </c>
+      <c r="E866" t="n">
+        <v>530</v>
+      </c>
+      <c r="F866" t="n">
+        <v>22</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>8</v>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>4</v>
+      </c>
+      <c r="E867" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F867" t="n">
+        <v>118</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>9</v>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D868" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E868" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F868" t="n">
+        <v>135</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>10</v>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D869" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E869" t="n">
+        <v>870</v>
+      </c>
+      <c r="F869" t="n">
+        <v>46</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>11</v>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D870" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E870" t="n">
+        <v>12</v>
+      </c>
+      <c r="F870" t="n">
+        <v>1</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>8.33%</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>12</v>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E871" t="n">
+        <v>480</v>
+      </c>
+      <c r="F871" t="n">
+        <v>18</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>13</v>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D872" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E872" t="n">
+        <v>4</v>
+      </c>
+      <c r="F872" t="n">
+        <v>1</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>14</v>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D873" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E873" t="n">
+        <v>590</v>
+      </c>
+      <c r="F873" t="n">
+        <v>26</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>15</v>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D874" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E874" t="n">
+        <v>820</v>
+      </c>
+      <c r="F874" t="n">
+        <v>45</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>16</v>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D875" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E875" t="n">
+        <v>760</v>
+      </c>
+      <c r="F875" t="n">
+        <v>38</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B876" t="n">
+        <v>17</v>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D876" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E876" t="n">
+        <v>930</v>
+      </c>
+      <c r="F876" t="n">
+        <v>58</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B877" t="n">
+        <v>18</v>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D877" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E877" t="n">
+        <v>880</v>
+      </c>
+      <c r="F877" t="n">
+        <v>52</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B878" t="n">
+        <v>19</v>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D878" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E878" t="n">
+        <v>34</v>
+      </c>
+      <c r="F878" t="n">
+        <v>0</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="n">
+        <v>20</v>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D879" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E879" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F879" t="n">
+        <v>168</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B880" t="n">
+        <v>21</v>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D880" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E880" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F880" t="n">
+        <v>121</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B881" t="n">
+        <v>22</v>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D881" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E881" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F881" t="n">
+        <v>104</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>1</v>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D882" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E882" t="n">
+        <v>50</v>
+      </c>
+      <c r="F882" t="n">
+        <v>4</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B883" t="n">
+        <v>2</v>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D883" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E883" t="n">
+        <v>163</v>
+      </c>
+      <c r="F883" t="n">
+        <v>5</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>3</v>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D884" t="n">
+        <v>5</v>
+      </c>
+      <c r="E884" t="n">
+        <v>980</v>
+      </c>
+      <c r="F884" t="n">
+        <v>54</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>4</v>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D885" t="n">
+        <v>6</v>
+      </c>
+      <c r="E885" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F885" t="n">
+        <v>68</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>5</v>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D886" t="n">
+        <v>9</v>
+      </c>
+      <c r="E886" t="n">
+        <v>640</v>
+      </c>
+      <c r="F886" t="n">
+        <v>25</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>6</v>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D887" t="n">
+        <v>7</v>
+      </c>
+      <c r="E887" t="n">
+        <v>720</v>
+      </c>
+      <c r="F887" t="n">
+        <v>38</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>7</v>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D888" t="n">
+        <v>8</v>
+      </c>
+      <c r="E888" t="n">
+        <v>530</v>
+      </c>
+      <c r="F888" t="n">
+        <v>22</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>8</v>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D889" t="n">
+        <v>4</v>
+      </c>
+      <c r="E889" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F889" t="n">
+        <v>118</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>9</v>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D890" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E890" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F890" t="n">
+        <v>135</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>10</v>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D891" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E891" t="n">
+        <v>870</v>
+      </c>
+      <c r="F891" t="n">
+        <v>46</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>11</v>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D892" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E892" t="n">
+        <v>12</v>
+      </c>
+      <c r="F892" t="n">
+        <v>1</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>8.33%</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>12</v>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D893" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E893" t="n">
+        <v>480</v>
+      </c>
+      <c r="F893" t="n">
+        <v>18</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>13</v>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D894" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E894" t="n">
+        <v>4</v>
+      </c>
+      <c r="F894" t="n">
+        <v>1</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>14</v>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D895" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E895" t="n">
+        <v>590</v>
+      </c>
+      <c r="F895" t="n">
+        <v>26</v>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>15</v>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D896" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E896" t="n">
+        <v>820</v>
+      </c>
+      <c r="F896" t="n">
+        <v>45</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>16</v>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D897" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E897" t="n">
+        <v>760</v>
+      </c>
+      <c r="F897" t="n">
+        <v>38</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>17</v>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D898" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E898" t="n">
+        <v>930</v>
+      </c>
+      <c r="F898" t="n">
+        <v>58</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>18</v>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D899" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E899" t="n">
+        <v>880</v>
+      </c>
+      <c r="F899" t="n">
+        <v>52</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>19</v>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D900" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E900" t="n">
+        <v>34</v>
+      </c>
+      <c r="F900" t="n">
+        <v>0</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>20</v>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D901" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E901" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F901" t="n">
+        <v>168</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>21</v>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D902" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E902" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F902" t="n">
+        <v>121</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>22</v>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D903" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E903" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F903" t="n">
+        <v>104</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>1</v>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>mô hình quy hoạch</t>
+        </is>
+      </c>
+      <c r="D904" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E904" t="n">
+        <v>58</v>
+      </c>
+      <c r="F904" t="n">
+        <v>7</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>12.07%</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/danh-muc-du-an/mo-hinh-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>2</v>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D905" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E905" t="n">
+        <v>183</v>
+      </c>
+      <c r="F905" t="n">
+        <v>5</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>3</v>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>mô hình cao tầng</t>
+        </is>
+      </c>
+      <c r="D906" t="n">
+        <v>5</v>
+      </c>
+      <c r="E906" t="n">
+        <v>980</v>
+      </c>
+      <c r="F906" t="n">
+        <v>54</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>5.51%</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>4</v>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>mô hình nhà máy</t>
+        </is>
+      </c>
+      <c r="D907" t="n">
+        <v>6</v>
+      </c>
+      <c r="E907" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F907" t="n">
+        <v>68</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-nha-may/</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>5</v>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>mô hình thiết bị</t>
+        </is>
+      </c>
+      <c r="D908" t="n">
+        <v>9</v>
+      </c>
+      <c r="E908" t="n">
+        <v>640</v>
+      </c>
+      <c r="F908" t="n">
+        <v>25</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-3d/</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>6</v>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>mô hình trường học</t>
+        </is>
+      </c>
+      <c r="D909" t="n">
+        <v>7</v>
+      </c>
+      <c r="E909" t="n">
+        <v>720</v>
+      </c>
+      <c r="F909" t="n">
+        <v>38</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>5.28%</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>7</v>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>mô hình bệnh viện</t>
+        </is>
+      </c>
+      <c r="D910" t="n">
+        <v>8</v>
+      </c>
+      <c r="E910" t="n">
+        <v>530</v>
+      </c>
+      <c r="F910" t="n">
+        <v>22</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>4.15%</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/mo-hinh-tod-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>8</v>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>sa bàn quy hoạch</t>
+        </is>
+      </c>
+      <c r="D911" t="n">
+        <v>4</v>
+      </c>
+      <c r="E911" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F911" t="n">
+        <v>118</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/dich-vu-lam-sa-ban-quy-hoach/</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>9</v>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E912" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F912" t="n">
+        <v>135</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>10</v>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>sa bàn cao tầng</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E913" t="n">
+        <v>870</v>
+      </c>
+      <c r="F913" t="n">
+        <v>46</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-cao-tang/</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>11</v>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>sa bàn nhà máy</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E914" t="n">
+        <v>15</v>
+      </c>
+      <c r="F914" t="n">
+        <v>1</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/thi-cong-sa-ban-nha-may-khu-cong-nghiep/</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>12</v>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>sa bàn thiết bị</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E915" t="n">
+        <v>480</v>
+      </c>
+      <c r="F915" t="n">
+        <v>18</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sa-ban-noi-that/</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>13</v>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>sa bàn trường học</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E916" t="n">
+        <v>5</v>
+      </c>
+      <c r="F916" t="n">
+        <v>1</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban-truong-hoc/</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>14</v>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>sa bàn bệnh viện</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E917" t="n">
+        <v>590</v>
+      </c>
+      <c r="F917" t="n">
+        <v>26</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/du-an-noi-bat/</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>15</v>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>vận chuyển mô hình</t>
+        </is>
+      </c>
+      <c r="D918" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E918" t="n">
+        <v>820</v>
+      </c>
+      <c r="F918" t="n">
+        <v>45</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>16</v>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>vận chuyển sa bàn</t>
+        </is>
+      </c>
+      <c r="D919" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E919" t="n">
+        <v>760</v>
+      </c>
+      <c r="F919" t="n">
+        <v>38</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/van-chuyen-sa-ban-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>17</v>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>sửa chữa mô hình</t>
+        </is>
+      </c>
+      <c r="D920" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E920" t="n">
+        <v>930</v>
+      </c>
+      <c r="F920" t="n">
+        <v>58</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>18</v>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>sửa chữa sa bàn</t>
+        </is>
+      </c>
+      <c r="D921" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E921" t="n">
+        <v>880</v>
+      </c>
+      <c r="F921" t="n">
+        <v>52</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/sua-chua-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>19</v>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>công ty mô hình kiến trúc</t>
+        </is>
+      </c>
+      <c r="D922" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E922" t="n">
+        <v>43</v>
+      </c>
+      <c r="F922" t="n">
+        <v>1</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/cong-ty-lam-mo-hinh/</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>🖼️ Image Pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>20</v>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>công ty sa bàn kiến trúc</t>
+        </is>
+      </c>
+      <c r="D923" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E923" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F923" t="n">
+        <v>168</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B924" t="n">
+        <v>21</v>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>làm mô hình</t>
+        </is>
+      </c>
+      <c r="D924" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E924" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F924" t="n">
+        <v>121</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-mo-hinh-kien-truc/</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B925" t="n">
+        <v>22</v>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>làm sa bàn</t>
+        </is>
+      </c>
+      <c r="D925" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E925" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F925" t="n">
+        <v>104</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>https://mohinhkientruc.org/lam-sa-ban/</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Standard Snippet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
